--- a/W2D1.xlsx
+++ b/W2D1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miche\Desktop\Master in Ai Epicode\Esercizi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EBF3DE-F624-41F4-A6CE-113F490BDA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F39704-6D43-4507-8F46-CE485444BB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,6 +79,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -126,7 +132,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -134,22 +140,120 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{430581DC-F5A6-4F8A-93B5-3B1A2421D22C}">
-  <dimension ref="B3:I30"/>
+  <dimension ref="B3:K86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
@@ -472,353 +576,797 @@
     <col min="18" max="18" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+    <row r="5" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C6">
-        <v>52</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="C6" s="13">
+        <f>AVERAGE($K$6:$K$86)</f>
+        <v>51.851851851851855</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>52</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="F6" s="13">
+        <f>AVERAGE($K$6:$K$86)</f>
+        <v>51.851851851851855</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I6">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="I6" s="14">
+        <f>AVERAGE($K$6:$K$86)</f>
+        <v>51.851851851851855</v>
+      </c>
+      <c r="K6" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="15">
         <v>9</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D7" s="15"/>
+      <c r="E7" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="15">
         <v>9</v>
       </c>
-      <c r="H7" t="s">
+      <c r="G7" s="15"/>
+      <c r="H7" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="K7" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="15">
         <v>81</v>
       </c>
-      <c r="E8" t="s">
+      <c r="D8" s="15"/>
+      <c r="E8" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="15">
         <v>81</v>
       </c>
-      <c r="H8" t="s">
+      <c r="G8" s="15"/>
+      <c r="H8" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="5">
         <v>81</v>
       </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+      <c r="K8" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="15">
         <v>0.9</v>
       </c>
-      <c r="E9" t="s">
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="15">
         <v>0.95</v>
       </c>
-      <c r="H9" t="s">
+      <c r="G9" s="15"/>
+      <c r="H9" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="5">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+      <c r="K9" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="5"/>
+      <c r="K10" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="21">
         <f>1-C9</f>
         <v>9.9999999999999978E-2</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="15"/>
+      <c r="E11" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="22">
         <f>1-F9</f>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="G11" s="15"/>
+      <c r="H11" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="7">
         <f>1-I9</f>
         <v>1.0000000000000009E-2</v>
       </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+      <c r="K11" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="5"/>
+      <c r="K12" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="20">
         <f>_xlfn.CONFIDENCE.NORM(C11,C7,C8)</f>
         <v>1.6448536269514715</v>
       </c>
-      <c r="E13" t="s">
+      <c r="D13" s="15"/>
+      <c r="E13" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="20">
         <f>_xlfn.CONFIDENCE.NORM(F11,F7,F8)</f>
         <v>1.9599639845400536</v>
       </c>
-      <c r="H13" t="s">
+      <c r="G13" s="15"/>
+      <c r="H13" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="8">
         <f>_xlfn.CONFIDENCE.NORM(I11,I7,I8)</f>
         <v>2.5758293035488999</v>
       </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+      <c r="K13" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="1">
-        <f>C8-C13</f>
-        <v>79.355146373048527</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="C14" s="20">
+        <f>C6-C13</f>
+        <v>50.206998224900381</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="1">
-        <f>F8-F13</f>
-        <v>79.040036015459947</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="F14" s="20">
+        <f>F6-F13</f>
+        <v>49.891887867311802</v>
+      </c>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I14" s="1">
-        <f>I8-I13</f>
-        <v>78.4241706964511</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
+      <c r="I14" s="8">
+        <f>I6-I13</f>
+        <v>49.276022548302954</v>
+      </c>
+      <c r="K14" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="1">
-        <f>C8+C13</f>
-        <v>82.644853626951473</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="C15" s="10">
+        <f>C6+C13</f>
+        <v>53.496705478803328</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="1">
-        <f>F8+F13</f>
-        <v>82.959963984540053</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="F15" s="10">
+        <f>F6+F13</f>
+        <v>53.811815836391908</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="1">
-        <f>I8+I13</f>
-        <v>83.5758293035489</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
+      <c r="I15" s="12">
+        <f>I6+I13</f>
+        <v>54.427681155400755</v>
+      </c>
+      <c r="K15" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K16" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K17" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K18" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K19" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C21">
-        <v>52</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="C21" s="13">
+        <f>AVERAGE($K$6:$K$86)</f>
+        <v>51.851851851851855</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F21">
-        <v>52</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="F21" s="13">
+        <f>AVERAGE($K$6:$K$86)</f>
+        <v>51.851851851851855</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I21">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
+      <c r="I21" s="14">
+        <f>AVERAGE($K$6:$K$86)</f>
+        <v>51.851851851851855</v>
+      </c>
+      <c r="K21" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B22" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="15">
         <v>9</v>
       </c>
-      <c r="E22" t="s">
+      <c r="D22" s="15"/>
+      <c r="E22" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="15">
         <v>9</v>
       </c>
-      <c r="H22" t="s">
+      <c r="G22" s="15"/>
+      <c r="H22" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+      <c r="K22" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="15">
         <v>324</v>
       </c>
-      <c r="E23" t="s">
+      <c r="D23" s="15"/>
+      <c r="E23" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="15">
         <v>324</v>
       </c>
-      <c r="H23" t="s">
+      <c r="G23" s="15"/>
+      <c r="H23" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="5">
         <v>324</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
+      <c r="K23" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B24" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="15">
         <v>0.9</v>
       </c>
-      <c r="E24" t="s">
+      <c r="D24" s="15"/>
+      <c r="E24" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="15">
         <v>0.95</v>
       </c>
-      <c r="H24" t="s">
+      <c r="G24" s="15"/>
+      <c r="H24" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="5">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
+      <c r="K24" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B25" s="4"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="5"/>
+      <c r="K25" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="16">
         <f>1-C24</f>
         <v>9.9999999999999978E-2</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="D26" s="15"/>
+      <c r="E26" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="18">
         <f>1-F24</f>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="G26" s="15"/>
+      <c r="H26" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="19">
         <f>1-I24</f>
         <v>1.0000000000000009E-2</v>
       </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
+      <c r="K26" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B27" s="4"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="5"/>
+      <c r="K27" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="20">
         <f>_xlfn.CONFIDENCE.NORM(C26,C22,C23)</f>
         <v>0.82242681347573576</v>
       </c>
-      <c r="E28" t="s">
+      <c r="D28" s="15"/>
+      <c r="E28" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="20">
         <f>_xlfn.CONFIDENCE.NORM(F26,F22,F23)</f>
         <v>0.9799819922700268</v>
       </c>
-      <c r="H28" t="s">
+      <c r="G28" s="15"/>
+      <c r="H28" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I28" s="8">
         <f>_xlfn.CONFIDENCE.NORM(I26,I22,I23)</f>
         <v>1.28791465177445</v>
       </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
+      <c r="K28" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="1">
-        <f>C23-C28</f>
-        <v>323.17757318652428</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="C29" s="20">
+        <f>C21-C28</f>
+        <v>51.029425038376118</v>
+      </c>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F29" s="1">
-        <f>F23-F28</f>
-        <v>323.02001800772996</v>
-      </c>
-      <c r="H29" t="s">
+      <c r="F29" s="20">
+        <f>F21-F28</f>
+        <v>50.871869859581828</v>
+      </c>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I29" s="1">
-        <f>I23-I28</f>
-        <v>322.71208534822557</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
+      <c r="I29" s="8">
+        <f>I21-I28</f>
+        <v>50.563937200077405</v>
+      </c>
+      <c r="K29" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="1">
-        <f>C23+C28</f>
-        <v>324.82242681347572</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="C30" s="10">
+        <f>C21+C28</f>
+        <v>52.674278665327591</v>
+      </c>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="1">
-        <f>F23+F28</f>
-        <v>324.97998199227004</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="F30" s="10">
+        <f>F21+F28</f>
+        <v>52.831833844121881</v>
+      </c>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="I30" s="1">
-        <f>I23+I28</f>
-        <v>325.28791465177443</v>
+      <c r="I30" s="12">
+        <f>I21+I28</f>
+        <v>53.139766503626305</v>
+      </c>
+      <c r="K30" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K31" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K32" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K33" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K34" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K35" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K36" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K37" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K38" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K39" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K40" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K41" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K42" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K43" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K44" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K45" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K46" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K47" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K48" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K49" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K50" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K51" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K52" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K53" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K54" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K55" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K56" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K57" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K58" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K59" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K60" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K61" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K62" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="63" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K63" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K64" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="65" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K65" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K66" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="67" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K67" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K68" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="69" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K69" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K70" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K71" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="72" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K72" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="73" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K73" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="74" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K74" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="75" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K75" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="76" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K76" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="77" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K77" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K78" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="79" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K79" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="80" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K80" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="81" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K81" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="82" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K82" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="83" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K83" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="84" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K84" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="85" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K85" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86" spans="11:11" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="K86" s="1">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
